--- a/test-cases/test-cases.xlsx
+++ b/test-cases/test-cases.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="ปิดจบ Phase 1 ออกแบบ Test Cases" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="ปรับปรุง Test Case ตามหลักการ W" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -11,282 +11,513 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="92">
-  <si>
-    <t>Test ID</t>
-  </si>
-  <si>
-    <t>Module</t>
-  </si>
-  <si>
-    <t>Test Scenario (กรณีทดสอบ)</t>
-  </si>
-  <si>
-    <t>Test Data (ข้อมูลทดสอบ)</t>
-  </si>
-  <si>
-    <t>Expected Result (ผลที่คาดหวัง)</t>
-  </si>
-  <si>
-    <t>Test Type</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="169">
+  <si>
+    <t>Test Case ID</t>
+  </si>
+  <si>
+    <t>Test Case Title</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Priority</t>
+  </si>
+  <si>
+    <t>Preconditions</t>
+  </si>
+  <si>
+    <t>Test Data</t>
+  </si>
+  <si>
+    <t>Test Steps</t>
+  </si>
+  <si>
+    <t>Expected Results</t>
+  </si>
+  <si>
+    <t>Actual Results</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Postconditions</t>
   </si>
   <si>
     <t>TC-001</t>
   </si>
   <si>
-    <t>Auth</t>
-  </si>
-  <si>
-    <t>Login ด้วยรหัสผ่านที่ผิด</t>
-  </si>
-  <si>
-    <t>User: admin, Pass: wrong123</t>
-  </si>
-  <si>
-    <t>ระบบปฏิเสธการเข้าถึง และแจ้งเตือน "รหัสผ่านไม่ถูกต้อง"</t>
-  </si>
-  <si>
-    <t>Functional</t>
+    <t>Login fail with invalid password</t>
+  </si>
+  <si>
+    <t>ทดสอบระบบปฏิเสธการล็อกอินเมื่อรหัสผ่านผิด</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>อยู่หน้า Login, บัญชี admin มีอยู่จริง</t>
+  </si>
+  <si>
+    <t>User: adminPass: wrong123</t>
+  </si>
+  <si>
+    <t>1. ไปที่หน้า Login2. กรอก Username3. กรอก Password ผิด4. คลิก Login</t>
+  </si>
+  <si>
+    <t>1. ล็อกอินไม่สำเร็จ2. แสดงข้อความ "รหัสผ่านไม่ถูกต้อง"3. ยังคงอยู่หน้า Login</t>
+  </si>
+  <si>
+    <t>Not Run</t>
+  </si>
+  <si>
+    <t>สถานะยังเป็น Logged out</t>
   </si>
   <si>
     <t>TC-002</t>
   </si>
   <si>
-    <t>[Security] SQL Injection ผ่านช่อง Username</t>
-  </si>
-  <si>
-    <t>User: ' OR '1'='1, Pass: any</t>
-  </si>
-  <si>
-    <t>ระบบปฏิเสธการเข้าถึง ไม่ยอมให้ Login ทะลุเข้าไป</t>
-  </si>
-  <si>
-    <t>Security</t>
+    <t>Security - SQLi on Login</t>
+  </si>
+  <si>
+    <t>ทดสอบป้องกัน SQL Injection ที่ช่อง Username</t>
+  </si>
+  <si>
+    <t>Critical</t>
+  </si>
+  <si>
+    <t>อยู่หน้า Login, สถานะ Logged out</t>
+  </si>
+  <si>
+    <t>User: ' OR '1'='1Pass: any</t>
+  </si>
+  <si>
+    <t>1. ไปที่หน้า Login2. กรอก SQLi Payload ใน Username3. กรอกรหัสผ่านมั่ว4. คลิก Login</t>
+  </si>
+  <si>
+    <t>1. ล็อกอินไม่สำเร็จ2. ไม่เกิด Database Error3. แสดงข้อความเตือนปกติ</t>
+  </si>
+  <si>
+    <t>ไม่มีข้อมูล DB เปลี่ยนแปลง</t>
   </si>
   <si>
     <t>TC-003</t>
   </si>
   <si>
-    <t>[Security] ตรวจสอบการป้องกัน Brute Force</t>
-  </si>
-  <si>
-    <t>พยายาม Login ผิด 5 ครั้งติดกัน</t>
-  </si>
-  <si>
-    <t>ระบบระงับบัญชีชั่วคราว หรือ Delay การตอบสนอง</t>
+    <t>Security - Brute Force Protection</t>
+  </si>
+  <si>
+    <t>ทดสอบระบบป้องกันการสุ่มเดารหัสผ่านซ้ำๆ</t>
+  </si>
+  <si>
+    <t>อยู่หน้า Login, บัญชี testuser มีอยู่จริง</t>
+  </si>
+  <si>
+    <t>User: testuserPass: (สุ่มผิด 5 ครั้ง)</t>
+  </si>
+  <si>
+    <t>1. ไปที่หน้า Login2. กรอกรหัสผ่านผิด 5 ครั้งติดกันภายใน 1 นาที</t>
+  </si>
+  <si>
+    <t>1. ครั้งที่ 6 ระบบบล็อกการล็อกอิน2. แจ้งเตือน "บัญชีถูกระงับชั่วคราว"</t>
+  </si>
+  <si>
+    <t>บัญชี testuser ถูกระงับชั่วคราว</t>
   </si>
   <si>
     <t>TC-004</t>
   </si>
   <si>
-    <t>Register ด้วยรหัสผ่านที่อ่อนแอ</t>
-  </si>
-  <si>
-    <t>Pass: 12345</t>
-  </si>
-  <si>
-    <t>ระบบปฏิเสธ และแจ้งว่าต้องยาว 8 ตัวอักษรขึ้นไป</t>
+    <t>Security - XSS on Registration</t>
+  </si>
+  <si>
+    <t>ทดสอบป้องกัน XSS Injection ที่ช่องชื่อ</t>
+  </si>
+  <si>
+    <t>อยู่หน้า Register</t>
+  </si>
+  <si>
+    <t>Name: &lt;script&gt;alert(1)&lt;/script&gt;User: xss1Pass: Pass@123</t>
+  </si>
+  <si>
+    <t>1. ไปที่หน้า Register2. กรอก XSS Payload ในช่องชื่อ3. กรอกข้อมูลอื่นให้ครบ4. คลิก Register</t>
+  </si>
+  <si>
+    <t>1. ระบบบันทึกสำเร็จแต่แปลง Tag (Sanitize)2. เมื่อดึงชื่อมาแสดง Script ต้องไม่ทำงาน</t>
+  </si>
+  <si>
+    <t>มี User ใหม่ แต่ชื่อถูกเข้ารหัส HTML Entity</t>
   </si>
   <si>
     <t>TC-005</t>
   </si>
   <si>
-    <t>[Security] XSS Injection ผ่านช่อง ชื่อผู้ใช้</t>
-  </si>
-  <si>
-    <t>Name: &lt;script&gt;alert(1)&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>ระบบต้อง Sanitize ข้อความ หรือปฏิเสธข้อมูลนี้</t>
+    <t>Weak Password Rejection</t>
+  </si>
+  <si>
+    <t>ทดสอบการปฏิเสธรหัสผ่านที่สั้นเกินไป</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>User: newuserPass: 1234</t>
+  </si>
+  <si>
+    <t>1. ไปที่หน้า Register2. กรอก User ปกติ3. กรอกรหัสสั้น (4 ตัว)4. คลิก Register</t>
+  </si>
+  <si>
+    <t>1. สมัครไม่สำเร็จ2. แจ้งเตือน "รหัสผ่านต้องมี 8 ตัวอักษรขึ้นไป"</t>
+  </si>
+  <si>
+    <t>ไม่มี User ใหม่ในระบบ</t>
   </si>
   <si>
     <t>TC-006</t>
   </si>
   <si>
-    <t>เข้าถึง API ส่วนตัวโดยไม่ส่ง Token</t>
-  </si>
-  <si>
-    <t>(ไม่มี Header Authorization)</t>
-  </si>
-  <si>
-    <t>แจ้ง HTTP 401 Unauthorized</t>
+    <t>Access API without Token</t>
+  </si>
+  <si>
+    <t>ทดสอบการป้องกัน API ลับเมื่อไม่มี Token</t>
+  </si>
+  <si>
+    <t>ไม่มี Token ในระบบ</t>
+  </si>
+  <si>
+    <t>API Endpoint: /api/books (POST)</t>
+  </si>
+  <si>
+    <t>1. ส่ง Request สร้างหนังสือใหม่โดยไม่แนบ Header Authorization</t>
+  </si>
+  <si>
+    <t>1. ปฏิเสธ Request2. ตอบกลับ HTTP 401 Unauthorized</t>
+  </si>
+  <si>
+    <t>ไม่มีหนังสือถูกเพิ่ม</t>
   </si>
   <si>
     <t>TC-007</t>
   </si>
   <si>
-    <t>เข้าถึง API ด้วย Token ที่หมดอายุแล้ว</t>
-  </si>
-  <si>
-    <t>ส่ง JWT ที่ Expire แล้ว</t>
+    <t>Access API with Expired Token</t>
+  </si>
+  <si>
+    <t>ทดสอบการปฏิเสธ JWT Token ที่หมดอายุ</t>
+  </si>
+  <si>
+    <t>มี Token ที่หมดอายุแล้วเตรียมไว้</t>
+  </si>
+  <si>
+    <t>Expired JWT Token</t>
+  </si>
+  <si>
+    <t>1. ส่ง Request ดึงข้อมูลส่วนตัว พร้อมแนบ Expired Token</t>
+  </si>
+  <si>
+    <t>1. ปฏิเสธ Request2. ตอบกลับ HTTP 401 (Token Expired)</t>
+  </si>
+  <si>
+    <t>ไม่สามารถดูข้อมูลส่วนตัวได้</t>
   </si>
   <si>
     <t>TC-008</t>
   </si>
   <si>
-    <t>[Security] ปลอมแปลง JWT Token (Tampering)</t>
-  </si>
-  <si>
-    <t>เปลี่ยน Payload ใน JWT เอง</t>
-  </si>
-  <si>
-    <t>แจ้ง HTTP 401 Unauthorized (Signature Invalid)</t>
+    <t>Security - JWT Tampering</t>
+  </si>
+  <si>
+    <t>ทดสอบระบบจับการปลอมแปลง JWT</t>
+  </si>
+  <si>
+    <t>มี Token ปกติของ User</t>
+  </si>
+  <si>
+    <t>Modified JWT (เปลี่ยน role จาก user เป็น admin)</t>
+  </si>
+  <si>
+    <t>1. แก้ไข Payload ใน Token2. ส่ง Request โดยใช้ Token ที่แก้แล้ว</t>
+  </si>
+  <si>
+    <t>1. ปฏิเสธ Request2. ตอบกลับ HTTP 401 (Signature Invalid)</t>
+  </si>
+  <si>
+    <t>สิทธิ์ยังคงเป็น User ปกติ</t>
   </si>
   <si>
     <t>TC-009</t>
   </si>
   <si>
-    <t>Borrowing</t>
-  </si>
-  <si>
-    <t>[Security] User ธรรมดาเรียกใช้ฟังก์ชัน Admin</t>
-  </si>
-  <si>
-    <t>ส่ง Token ของ User ไปที่ API Admin</t>
-  </si>
-  <si>
-    <t>แจ้ง HTTP 403 Forbidden (เช็คจาก BUG-001)</t>
+    <t>Security - Broken Access Control</t>
+  </si>
+  <si>
+    <t>ทดสอบ User ธรรมดาเรียก API ของ Admin</t>
+  </si>
+  <si>
+    <t>ล็อกอินเป็น User ปกติ, มี Token</t>
+  </si>
+  <si>
+    <t>API Endpoint: /api/admin/users</t>
+  </si>
+  <si>
+    <t>1. ส่ง Request เข้าถึงเมนู Admin พร้อมแนบ Token ของ User ปกติ</t>
+  </si>
+  <si>
+    <t>1. ปฏิเสธ Request2. ตอบกลับ HTTP 403 Forbidden</t>
+  </si>
+  <si>
+    <t>ไม่สามารถดึงรายชื่อ User ได้</t>
   </si>
   <si>
     <t>TC-010</t>
   </si>
   <si>
-    <t>Admin เรียกใช้ฟังก์ชันจัดการการยืม</t>
-  </si>
-  <si>
-    <t>ส่ง Token ของ Admin</t>
-  </si>
-  <si>
-    <t>ทำรายการสำเร็จ (HTTP 200)</t>
+    <t>Admin Access Borrowing API</t>
+  </si>
+  <si>
+    <t>ทดสอบ Admin เรียกใช้งานระบบยืมคืน</t>
+  </si>
+  <si>
+    <t>ล็อกอินเป็น Admin</t>
+  </si>
+  <si>
+    <t>Token ของ Admin</t>
+  </si>
+  <si>
+    <t>1. ส่ง Request จัดการยืมหนังสือพร้อมแนบ Token Admin</t>
+  </si>
+  <si>
+    <t>1. อนุมัติ Request2. ตอบกลับ HTTP 200 OK</t>
+  </si>
+  <si>
+    <t>ทำรายการยืมหนังสือสำเร็จ</t>
   </si>
   <si>
     <t>TC-011</t>
   </si>
   <si>
-    <t>[Security] IDOR: ยืมหนังสือในชื่อคนอื่น</t>
-  </si>
-  <si>
-    <t>แก้ไข userId ใน Request Body</t>
-  </si>
-  <si>
-    <t>ระบบต้องเช็คว่า userId ตรงกับ Token หรือไม่</t>
+    <t>Security - IDOR on Profile</t>
+  </si>
+  <si>
+    <t>ทดสอบการแอบดูข้อมูลโปรไฟล์คนอื่น (IDOR)</t>
+  </si>
+  <si>
+    <t>ล็อกอินเป็น User (ID: 1)</t>
+  </si>
+  <si>
+    <t>API Endpoint: /api/users/2</t>
+  </si>
+  <si>
+    <t>1. ส่ง Request ขอดูข้อมูล User ID 2 โดยใช้ Token ของ User ID 1</t>
+  </si>
+  <si>
+    <t>1. ปฏิเสธ Request2. ตอบกลับ HTTP 403 (Unauthorized Access)</t>
+  </si>
+  <si>
+    <t>ไม่เห็นข้อมูลของ User 2</t>
   </si>
   <si>
     <t>TC-012</t>
   </si>
   <si>
-    <t>Books</t>
-  </si>
-  <si>
-    <t>ค้นหาหนังสือตามปกติ</t>
-  </si>
-  <si>
-    <t>Keyword: "Harry Potter"</t>
-  </si>
-  <si>
-    <t>แสดงรายการหนังสือที่ตรงกัน</t>
+    <t>Search existing book</t>
+  </si>
+  <si>
+    <t>ทดสอบฟังก์ชันค้นหาหนังสือปกติ</t>
+  </si>
+  <si>
+    <t>มีหนังสือ "Harry" ในระบบ</t>
+  </si>
+  <si>
+    <t>Keyword: "Harry"</t>
+  </si>
+  <si>
+    <t>1. ไปหน้าค้นหา2. กรอก "Harry"3. กดค้นหา</t>
+  </si>
+  <si>
+    <t>1. แสดงรายชื่อหนังสือที่มีคำว่า Harry2. หน้าตาเว็บแสดงผลปกติ</t>
+  </si>
+  <si>
+    <t>การค้นหาเสร็จสิ้น</t>
   </si>
   <si>
     <t>TC-013</t>
   </si>
   <si>
-    <t>[Security] SQL Injection ในช่องค้นหา</t>
+    <t>Security - SQLi on Search</t>
+  </si>
+  <si>
+    <t>ทดสอบป้องกัน SQL Injection ช่องค้นหา</t>
+  </si>
+  <si>
+    <t>อยู่หน้าค้นหาหนังสือ</t>
   </si>
   <si>
     <t>Keyword: %; DROP TABLE books;--</t>
   </si>
   <si>
-    <t>ระบบกรองคำสั่งทิ้ง และไม่เกิด Error ฐานข้อมูล</t>
+    <t>1. ไปหน้าค้นหา2. กรอก Payload SQLi ลงในช่องค้นหา3. กดค้นหา</t>
+  </si>
+  <si>
+    <t>1. ไม่เกิด Error ฐานข้อมูล2. กรองคำสั่งทิ้ง หรือแสดงผล "ไม่พบหนังสือ"</t>
+  </si>
+  <si>
+    <t>โครงสร้าง Database ยังคงเดิม</t>
   </si>
   <si>
     <t>TC-014</t>
   </si>
   <si>
-    <t>เพิ่มหนังสือใหม่ (สิทธิ์ Admin)</t>
-  </si>
-  <si>
-    <t>ข้อมูลหนังสือครบถ้วน</t>
-  </si>
-  <si>
-    <t>บันทึกสำเร็จ (HTTP 201)</t>
+    <t>Add valid book</t>
+  </si>
+  <si>
+    <t>ทดสอบฟังก์ชันเพิ่มหนังสือโดย Admin</t>
+  </si>
+  <si>
+    <t>Title: "QA Book", Stock: 5</t>
+  </si>
+  <si>
+    <t>1. ไปหน้าจัดการหนังสือ2. กรอกข้อมูลหนังสือ3. กดบันทึก</t>
+  </si>
+  <si>
+    <t>1. บันทึกสำเร็จ2. แสดงข้อความ "เพิ่มหนังสือสำเร็จ"</t>
+  </si>
+  <si>
+    <t>มีหนังสือใหม่ใน Database</t>
   </si>
   <si>
     <t>TC-015</t>
   </si>
   <si>
-    <t>[Security] Stored XSS ในรายละเอียดหนังสือ</t>
+    <t>Security - Stored XSS Book Details</t>
+  </si>
+  <si>
+    <t>ทดสอบป้องกัน XSS ฝังในรายละเอียดหนังสือ</t>
   </si>
   <si>
     <t>Desc: &lt;img src=x onerror=alert('XSS')&gt;</t>
   </si>
   <si>
-    <t>ข้อความถูกแปลง (Escape) เมื่อดึงไปแสดงผล</t>
+    <t>1. เพิ่มหนังสือใหม่2. ใส่ Payload XSS ในช่องรายละเอียด3. เปิดดูหน้าหนังสือที่เพิ่งเพิ่ม</t>
+  </si>
+  <si>
+    <t>1. บันทึกได้2. ตอนแสดงผล Script ต้องไม่ทำงาน (รูปแตกหรือขึ้นเป็นข้อความแทน)</t>
+  </si>
+  <si>
+    <t>ข้อมูลถูกบันทึกแบบปลอดภัย</t>
   </si>
   <si>
     <t>TC-016</t>
   </si>
   <si>
-    <t>ลบหนังสือ (สิทธิ์ User ธรรมดา)</t>
-  </si>
-  <si>
-    <t>ส่งคำสั่ง DELETE ไปที่ API</t>
-  </si>
-  <si>
-    <t>แจ้ง HTTP 403 Forbidden</t>
+    <t>User Delete Book</t>
+  </si>
+  <si>
+    <t>ทดสอบป้องกัน User ธรรมดาลบหนังสือ</t>
+  </si>
+  <si>
+    <t>ล็อกอินเป็น User ปกติ</t>
+  </si>
+  <si>
+    <t>API: DELETE /api/books/1</t>
+  </si>
+  <si>
+    <t>1. ส่งคำสั่ง DELETE หนังสือผ่าน API (Postman) โดยใช้ Token User</t>
+  </si>
+  <si>
+    <t>หนังสือยังอยู่ในระบบ</t>
   </si>
   <si>
     <t>TC-017</t>
   </si>
   <si>
-    <t>Upload</t>
-  </si>
-  <si>
-    <t>อัปโหลดรูปโปรไฟล์ที่ถูกต้อง</t>
+    <t>Upload valid profile picture</t>
+  </si>
+  <si>
+    <t>ทดสอบอัปโหลดรูปภาพปกติ</t>
+  </si>
+  <si>
+    <t>ล็อกอินสำเร็จ, อยู่หน้าโปรไฟล์</t>
   </si>
   <si>
     <t>ไฟล์รูป profile.jpg</t>
   </si>
   <si>
-    <t>อัปโหลดสำเร็จ</t>
+    <t>1. กดเปลี่ยนรูปโปรไฟล์2. เลือกไฟล์ .jpg3. กดยืนยัน</t>
+  </si>
+  <si>
+    <t>1. อัปโหลดสำเร็จ2. รูปโปรไฟล์อัปเดตบนหน้าจอ</t>
+  </si>
+  <si>
+    <t>รูปถูกบันทึกในเซิร์ฟเวอร์</t>
   </si>
   <si>
     <t>TC-018</t>
   </si>
   <si>
-    <t>[Security] อัปโหลดไฟล์อันตราย (Malicious File)</t>
-  </si>
-  <si>
-    <t>ไฟล์สคริปต์ shell.php</t>
-  </si>
-  <si>
-    <t>ระบบปฏิเสธการอัปโหลดไฟล์ประเภทนี้</t>
+    <t>Security - Malicious File Upload</t>
+  </si>
+  <si>
+    <t>ทดสอบป้องกันการอัปโหลดไฟล์สคริปต์อันตราย</t>
+  </si>
+  <si>
+    <t>ไฟล์ shell.php</t>
+  </si>
+  <si>
+    <t>1. กดเปลี่ยนรูปโปรไฟล์2. เลือกไฟล์นามสกุล .php3. กดยืนยัน</t>
+  </si>
+  <si>
+    <t>1. ระบบปฏิเสธไฟล์2. แจ้งเตือน "อนุญาตเฉพาะไฟล์รูปภาพเท่านั้น"</t>
+  </si>
+  <si>
+    <t>ไฟล์สคริปต์ไม่ถูกเซฟลงเซิร์ฟเวอร์</t>
   </si>
   <si>
     <t>TC-019</t>
   </si>
   <si>
-    <t>Dashboard</t>
-  </si>
-  <si>
-    <t>เรียกดูสถิติ (สิทธิ์ Admin)</t>
+    <t>View Dashboard Stats</t>
+  </si>
+  <si>
+    <t>ทดสอบเรียกดูสถิติ (สำหรับ Admin)</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>แสดงผลสถิติสำเร็จ</t>
+    <t>1. ไปที่หน้า Dashboard Admin</t>
+  </si>
+  <si>
+    <t>1. โหลดข้อมูลสำเร็จ2. แสดงกราฟหรือตัวเลขสถิติถูกต้อง</t>
+  </si>
+  <si>
+    <t>เข้าถึงข้อมูลสถิติได้</t>
   </si>
   <si>
     <t>TC-020</t>
   </si>
   <si>
-    <t>[Security] SQL Injection ใน Parameter วันที่</t>
+    <t>Security - SQLi on Date Parameter</t>
+  </si>
+  <si>
+    <t>ทดสอบป้องกัน SQLi ผ่านพารามิเตอร์ URL</t>
+  </si>
+  <si>
+    <t>ล็อกอินเป็น Admin, หน้า Dashboard</t>
   </si>
   <si>
     <t>Date: 2026-03-16' OR SLEEP(5)--</t>
   </si>
   <si>
-    <t>ปฏิเสธ Request และไม่เกิดการ Delay ของระบบ</t>
+    <t>1. เปลี่ยนค่าวันที่ใน URL (Parameter) เป็น Payload แบบ Delay Time</t>
+  </si>
+  <si>
+    <t>1. ระบบดักจับได้และคืนค่า HTTP 4002. ระบบไม่มีอาการค้างหรือ Delay 5 วินาที</t>
+  </si>
+  <si>
+    <t>เซิร์ฟเวอร์ทำงานลื่นไหลปกติ</t>
   </si>
 </sst>
 </file>
@@ -393,7 +624,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1">
-    <tableStyle count="4" pivot="0" name="ปิดจบ Phase 1 ออกแบบ Test Cases-style">
+    <tableStyle count="4" pivot="0" name="ปรับปรุง Test Case ตามหลักการ W-style">
       <tableStyleElement dxfId="1" type="headerRow"/>
       <tableStyleElement dxfId="2" type="firstRowStripe"/>
       <tableStyleElement dxfId="3" type="secondRowStripe"/>
@@ -412,16 +643,21 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:F21" displayName="Phase_One_Tests" name="Phase_One_Tests" id="1">
-  <tableColumns count="6">
-    <tableColumn name="Test ID" id="1"/>
-    <tableColumn name="Module" id="2"/>
-    <tableColumn name="Test Scenario (กรณีทดสอบ)" id="3"/>
-    <tableColumn name="Test Data (ข้อมูลทดสอบ)" id="4"/>
-    <tableColumn name="Expected Result (ผลที่คาดหวัง)" id="5"/>
-    <tableColumn name="Test Type" id="6"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:K21" displayName="Security_Test_Cases" name="Security_Test_Cases" id="1">
+  <tableColumns count="11">
+    <tableColumn name="Test Case ID" id="1"/>
+    <tableColumn name="Test Case Title" id="2"/>
+    <tableColumn name="Description" id="3"/>
+    <tableColumn name="Priority" id="4"/>
+    <tableColumn name="Preconditions" id="5"/>
+    <tableColumn name="Test Data" id="6"/>
+    <tableColumn name="Test Steps" id="7"/>
+    <tableColumn name="Expected Results" id="8"/>
+    <tableColumn name="Actual Results" id="9"/>
+    <tableColumn name="Status" id="10"/>
+    <tableColumn name="Postconditions" id="11"/>
   </tableColumns>
-  <tableStyleInfo name="ปิดจบ Phase 1 ออกแบบ Test Cases-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="ปรับปรุง Test Case ตามหลักการ W-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
 </file>
 
@@ -626,11 +862,14 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="14.25"/>
-    <col customWidth="1" min="3" max="3" width="35.88"/>
-    <col customWidth="1" min="4" max="4" width="31.25"/>
-    <col customWidth="1" min="5" max="5" width="37.63"/>
-    <col customWidth="1" min="6" max="6" width="15.88"/>
+    <col customWidth="1" min="1" max="1" width="15.0"/>
+    <col customWidth="1" min="2" max="2" width="28.25"/>
+    <col customWidth="1" min="3" max="3" width="35.5"/>
+    <col customWidth="1" min="4" max="4" width="13.88"/>
+    <col customWidth="1" min="5" max="5" width="28.38"/>
+    <col customWidth="1" min="6" max="8" width="37.63"/>
+    <col customWidth="1" min="9" max="9" width="16.13"/>
+    <col customWidth="1" min="11" max="11" width="31.88"/>
   </cols>
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
@@ -652,414 +891,666 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="2" ht="22.5" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>7</v>
+        <v>11</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>11</v>
+        <v>15</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="3" ht="22.5" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>7</v>
+        <v>21</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>14</v>
+        <v>23</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>16</v>
+        <v>25</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>7</v>
+        <v>30</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>19</v>
+        <v>32</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>16</v>
+        <v>33</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>7</v>
+        <v>38</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>39</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>23</v>
+        <v>40</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>16</v>
+        <v>41</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>7</v>
+        <v>46</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>47</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>27</v>
+        <v>48</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>49</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>16</v>
+        <v>41</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>7</v>
+        <v>54</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>55</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>31</v>
+        <v>56</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>16</v>
+        <v>57</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>7</v>
+        <v>62</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>35</v>
+        <v>64</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>16</v>
+        <v>65</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="9" ht="22.5" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>7</v>
+        <v>70</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>71</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>38</v>
+        <v>72</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>16</v>
+        <v>73</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>41</v>
+        <v>78</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>79</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>43</v>
+        <v>80</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>16</v>
+        <v>81</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>41</v>
+        <v>86</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>87</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>47</v>
+        <v>88</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>11</v>
+        <v>89</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="12" ht="22.5" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>41</v>
+        <v>94</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>95</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>51</v>
+        <v>96</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>16</v>
+        <v>97</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="13" ht="22.5" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>54</v>
+        <v>102</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>103</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>56</v>
+        <v>104</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>49</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>11</v>
+        <v>105</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="14" ht="22.5" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>54</v>
+        <v>110</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>111</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>60</v>
+        <v>112</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>16</v>
+        <v>113</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="15" ht="22.5" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>54</v>
+        <v>118</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>119</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>64</v>
+        <v>120</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>11</v>
+        <v>89</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="16" ht="22.5" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>54</v>
+        <v>125</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>126</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>68</v>
+        <v>127</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>16</v>
+        <v>89</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="17" ht="22.5" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>54</v>
+        <v>132</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>133</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>72</v>
+        <v>134</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>16</v>
+        <v>135</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="18" ht="22.5" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>75</v>
+        <v>139</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>140</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>77</v>
+        <v>141</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>49</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>11</v>
+        <v>142</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="19" ht="22.5" customHeight="1">
       <c r="A19" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>75</v>
+        <v>147</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>148</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>81</v>
+        <v>149</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>16</v>
+        <v>142</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="20" ht="22.5" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>84</v>
+        <v>154</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>155</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>86</v>
+        <v>156</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>49</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>11</v>
+        <v>89</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="21" ht="22.5" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>84</v>
+        <v>161</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>162</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>90</v>
+        <v>163</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>16</v>
+        <v>164</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>168</v>
       </c>
     </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showDropDown="1" showErrorMessage="1" sqref="B2:B21">
-      <formula1>"Auth,Borrowing,Books,Upload,Dashboard"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="1" showErrorMessage="1" sqref="F2:F21">
-      <formula1>"Functional,Security"</formula1>
+    <dataValidation type="list" allowBlank="1" showDropDown="1" showErrorMessage="1" sqref="D2:D21">
+      <formula1>"High,Critical,Medium"</formula1>
     </dataValidation>
   </dataValidations>
   <drawing r:id="rId1"/>

--- a/test-cases/test-cases.xlsx
+++ b/test-cases/test-cases.xlsx
@@ -1,17 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E245D16-4CA1-471C-B2C0-6E19FFB2FF1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="ปรับปรุง Test Case ตามหลักการ W" sheetId="1" r:id="rId5"/>
+    <sheet name="Test Cases" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="247">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -518,20 +532,255 @@
   </si>
   <si>
     <t>เซิร์ฟเวอร์ทำงานลื่นไหลปกติ</t>
+  </si>
+  <si>
+    <t>TC-021</t>
+  </si>
+  <si>
+    <t>Security - User Enumeration</t>
+  </si>
+  <si>
+    <t>ทดสอบป้องกันการเดาอีเมลผู้ใช้ในระบบจากหน้าลืมรหัสผ่าน</t>
+  </si>
+  <si>
+    <t>ผู้ใช้อยู่ที่หน้า "ลืมรหัสผ่าน" (Forgot Password)</t>
+  </si>
+  <si>
+    <t>Email: notexist@email.com (อีเมลที่ไม่มีจริง)</t>
+  </si>
+  <si>
+    <t>1. ไปหน้าลืมรหัสผ่าน2. ใส่อีเมลที่ไม่มีในระบบ3. กดส่งลิงก์รีเซ็ต</t>
+  </si>
+  <si>
+    <t>1. ระบบแสดงข้อความกลางๆ เช่น "หากมีอีเมลนี้ในระบบ เราได้ส่งลิงก์ไปให้แล้ว"2. ต้องไม่แสดงข้อความว่า "ไม่พบอีเมลนี้"</t>
+  </si>
+  <si>
+    <t>ไม่มีอีเมลถูกส่งออกไป</t>
+  </si>
+  <si>
+    <t>TC-022</t>
+  </si>
+  <si>
+    <t>Security - Mass Assignment Profile</t>
+  </si>
+  <si>
+    <t>ทดสอบป้องกันการแอบอัปเกรดสิทธิ์ตัวเองผ่าน API</t>
+  </si>
+  <si>
+    <t>JSON Body: {"name":"test","role":"admin"}</t>
+  </si>
+  <si>
+    <t>1. ใช้ Postman ส่ง API (PUT) แก้ไขข้อมูลส่วนตัว2. แอบแนบฟิลด์ "role": "admin" เข้าไป</t>
+  </si>
+  <si>
+    <t>1. บันทึกชื่อใหม่สำเร็จ2. ระบบต้องเพิกเฉยต่อฟิลด์ role3. สิทธิ์ยังเป็น User ปกติ</t>
+  </si>
+  <si>
+    <t>ชื่อเปลี่ยน แต่สิทธิ์ยังเหมือนเดิม</t>
+  </si>
+  <si>
+    <t>TC-023</t>
+  </si>
+  <si>
+    <t>Security - API Rate Limiting</t>
+  </si>
+  <si>
+    <t>ทดสอบการป้องกัน DoS / สแปม Request</t>
+  </si>
+  <si>
+    <t>ระบบทำงานปกติ</t>
+  </si>
+  <si>
+    <t>API Endpoint: /api/books (ยิง 100 ครั้งใน 1 วิ)</t>
+  </si>
+  <si>
+    <t>1. ใช้ Postman Runner หรือสคริปต์ยิง API ค้นหาหนังสือรัวๆ 100 ครั้งใน 1 วินาที</t>
+  </si>
+  <si>
+    <t>1. ช่วงแรกโหลดข้อมูลได้2. หลังจากเกิน Limit ระบบบล็อกและตอบกลับ HTTP 429 Too Many Requests</t>
+  </si>
+  <si>
+    <t>ระบบยังทำงานได้ปกติ ไม่ล่ม</t>
+  </si>
+  <si>
+    <t>TC-024</t>
+  </si>
+  <si>
+    <t>Security - Information Exposure</t>
+  </si>
+  <si>
+    <t>ทดสอบว่า Error ไม่หลุดข้อมูล Database ออกมา</t>
+  </si>
+  <si>
+    <t>Book ID = abc (ใส่ตัวอักษรแทนตัวเลข)</t>
+  </si>
+  <si>
+    <t>1. เรียก API ขอดูข้อมูลหนังสือ GET /api/books/abc</t>
+  </si>
+  <si>
+    <t>1. ปฏิเสธ Request2. ตอบ HTTP 400 Bad Request3. ไม่มี Stack Trace หรือ โค้ด SQL โผล่มาที่หน้าจอ</t>
+  </si>
+  <si>
+    <t>ไม่มีข้อมูลรั่วไหล</t>
+  </si>
+  <si>
+    <t>TC-025</t>
+  </si>
+  <si>
+    <t>Security - Path Traversal</t>
+  </si>
+  <si>
+    <t>ทดสอบการแอบดูไฟล์ระบบผ่าน API ดึงรูป</t>
+  </si>
+  <si>
+    <t>มีรูปภาพโปรไฟล์อยู่ในระบบ</t>
+  </si>
+  <si>
+    <t>URL: /images?file=../../../../etc/passwd</t>
+  </si>
+  <si>
+    <t>1. เรียก API ดูรูปภาพ2. แก้ไขพารามิเตอร์ไฟล์ให้เป็น Path ย้อนกลับไปดูไฟล์ระบบ</t>
+  </si>
+  <si>
+    <t>1. ระบบต้องกรอง Path2. ตอบ HTTP 403 Forbidden หรือ 404 Not Found</t>
+  </si>
+  <si>
+    <t>ไม่สามารถเข้าถึงไฟล์ระบบได้</t>
+  </si>
+  <si>
+    <t>TC-026</t>
+  </si>
+  <si>
+    <t>Business Logic - Borrow unavailable</t>
+  </si>
+  <si>
+    <t>ทดสอบลอจิกการยืมหนังสือที่ถูกยืมไปแล้ว (หมดสต็อก)</t>
+  </si>
+  <si>
+    <t>หนังสือ ID: 1 มีสถานะ "ถูกยืมแล้ว" หรือสต็อกเป็น 0</t>
+  </si>
+  <si>
+    <t>Book ID: 1</t>
+  </si>
+  <si>
+    <t>1. ล็อกอินเป็น User ปกติ2. ส่งคำสั่งกดยืมหนังสือ ID 1</t>
+  </si>
+  <si>
+    <t>1. ยืมไม่สำเร็จ2. ระบบแจ้งเตือน "หนังสือเล่มนี้ไม่พร้อมให้บริการ"</t>
+  </si>
+  <si>
+    <t>สต็อกหนังสือไม่ติดลบ</t>
+  </si>
+  <si>
+    <t>TC-027</t>
+  </si>
+  <si>
+    <t>Security - Token reuse after Logout</t>
+  </si>
+  <si>
+    <t>ทดสอบการจัดการ Session ที่ไม่ปลอดภัยหลัง Logout</t>
+  </si>
+  <si>
+    <t>ล็อกอินและเก็บ JWT Token ไว้</t>
+  </si>
+  <si>
+    <t>Token ที่เพิ่งถูกใช้งาน</t>
+  </si>
+  <si>
+    <t>1. ล็อกอินและก็อปปี้ Token ไว้2. กด Logout3. นำ Token เดิมไปยิง API ขอดูโปรไฟล์ผ่าน Postman</t>
+  </si>
+  <si>
+    <t>1. ระบบไม่อนุญาตให้ใช้ Token นั้นอีก2. ตอบ HTTP 401 Unauthorized</t>
+  </si>
+  <si>
+    <t>โทเคนถูกทำลายหรือแบล็คลิสต์</t>
+  </si>
+  <si>
+    <t>TC-028</t>
+  </si>
+  <si>
+    <t>Security - HTTP Method Tampering</t>
+  </si>
+  <si>
+    <t>ทดสอบส่ง Method ผิดประเภทไปที่ API</t>
+  </si>
+  <si>
+    <t>ทราบ Endpoint ของ API</t>
+  </si>
+  <si>
+    <t>ส่ง POST ไปที่ API GET /api/books</t>
+  </si>
+  <si>
+    <t>1. ใช้ Postman ส่ง Request แบบ POST (สร้างข้อมูล) ไปยัง URL ที่รับเฉพาะ GET</t>
+  </si>
+  <si>
+    <t>1. ระบบปฏิเสธคำสั่งทันที2. ตอบกลับด้วย HTTP 405 Method Not Allowed</t>
+  </si>
+  <si>
+    <t>ไม่มีข้อมูลถูกสร้างใหม่</t>
+  </si>
+  <si>
+    <t>TC-029</t>
+  </si>
+  <si>
+    <t>Security - XSS in SVG Upload</t>
+  </si>
+  <si>
+    <t>ทดสอบฝัง XSS ในไฟล์ภาพแบบ SVG</t>
+  </si>
+  <si>
+    <t>ล็อกอินเข้าสู่หน้าแก้ไขโปรไฟล์</t>
+  </si>
+  <si>
+    <t>ไฟล์ xss.svg ที่แอบฝัง &lt;script&gt; ไว้</t>
+  </si>
+  <si>
+    <t>1. อัปโหลดไฟล์รูป .svg อันตราย2. เปิดดูรูปภาพบน Browser</t>
+  </si>
+  <si>
+    <t>1. ระบบปฏิเสธไฟล์ .svg ตั้งแต่แรก หรือ2. ถ้าให้ผ่าน ต้อง Sanitize โค้ดอันตรายออก Script ต้องไม่ทำงาน</t>
+  </si>
+  <si>
+    <t>บัญชีผู้ใช้ยังปลอดภัยจาก XSS</t>
+  </si>
+  <si>
+    <t>TC-030</t>
+  </si>
+  <si>
+    <t>Security - CSRF on Password Change</t>
+  </si>
+  <si>
+    <t>ทดสอบการเปลี่ยนรหัสโดยไม่ส่งตัวป้องกัน CSRF</t>
+  </si>
+  <si>
+    <t>ล็อกอินสำเร็จ</t>
+  </si>
+  <si>
+    <t>Request การเปลี่ยนรหัสที่ไม่มี CSRF Token</t>
+  </si>
+  <si>
+    <t>1. ใช้ Postman จำลองการยิง API เปลี่ยนรหัสผ่าน2. ไม่แนบ CSRF Token ใน Header/Body</t>
+  </si>
+  <si>
+    <t>1. ระบบปฏิเสธคำสั่ง2. ตอบ HTTP 403 Forbidden3. แจ้งเตือน Invalid CSRF Token</t>
+  </si>
+  <si>
+    <t>รหัสผ่านยังคงเป็นรหัสเดิม</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -542,70 +791,37 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF356854"/>
-          <bgColor rgb="FF356854"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF6F8F9"/>
-          <bgColor rgb="FFF6F8F9"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <border>
         <left style="thin">
@@ -622,20 +838,48 @@
         </bottom>
       </border>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF6F8F9"/>
+          <bgColor rgb="FFF6F8F9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF356854"/>
+          <bgColor rgb="FF356854"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="1">
-    <tableStyle count="4" pivot="0" name="ปรับปรุง Test Case ตามหลักการ W-style">
-      <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="2" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
-      <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
+    <tableStyle name="รวม 30 Test Case Design-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
+      <tableStyleElement type="wholeTable" size="0" dxfId="0"/>
+      <tableStyleElement type="headerRow" dxfId="3"/>
+      <tableStyleElement type="firstRowStripe" dxfId="2"/>
+      <tableStyleElement type="secondRowStripe" dxfId="1"/>
     </tableStyle>
   </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -643,26 +887,26 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:K21" displayName="Security_Test_Cases" name="Security_Test_Cases" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Security_Test_Cases" displayName="Security_Test_Cases" ref="A1:K31">
   <tableColumns count="11">
-    <tableColumn name="Test Case ID" id="1"/>
-    <tableColumn name="Test Case Title" id="2"/>
-    <tableColumn name="Description" id="3"/>
-    <tableColumn name="Priority" id="4"/>
-    <tableColumn name="Preconditions" id="5"/>
-    <tableColumn name="Test Data" id="6"/>
-    <tableColumn name="Test Steps" id="7"/>
-    <tableColumn name="Expected Results" id="8"/>
-    <tableColumn name="Actual Results" id="9"/>
-    <tableColumn name="Status" id="10"/>
-    <tableColumn name="Postconditions" id="11"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Test Case ID"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Test Case Title"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Priority"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Preconditions"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Test Data"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Test Steps"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Expected Results"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Actual Results"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Status"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Postconditions"/>
   </tableColumns>
-  <tableStyleInfo name="ปรับปรุง Test Case ตามหลักการ W-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="รวม 30 Test Case Design-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -852,27 +1096,30 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:K31"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="15.0"/>
-    <col customWidth="1" min="2" max="2" width="28.25"/>
-    <col customWidth="1" min="3" max="3" width="35.5"/>
-    <col customWidth="1" min="4" max="4" width="13.88"/>
-    <col customWidth="1" min="5" max="5" width="28.38"/>
-    <col customWidth="1" min="6" max="8" width="37.63"/>
-    <col customWidth="1" min="9" max="9" width="16.13"/>
-    <col customWidth="1" min="11" max="11" width="31.88"/>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="28.28515625" customWidth="1"/>
+    <col min="3" max="3" width="35.42578125" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" customWidth="1"/>
+    <col min="5" max="5" width="28.42578125" customWidth="1"/>
+    <col min="6" max="8" width="37.5703125" customWidth="1"/>
+    <col min="9" max="9" width="16.140625" customWidth="1"/>
+    <col min="11" max="11" width="31.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" customHeight="1">
+    <row r="1" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -907,7 +1154,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" ht="22.5" customHeight="1">
+    <row r="2" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
@@ -939,7 +1186,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" ht="22.5" customHeight="1">
+    <row r="3" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>21</v>
       </c>
@@ -971,7 +1218,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" ht="22.5" customHeight="1">
+    <row r="4" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>30</v>
       </c>
@@ -1003,7 +1250,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="5" ht="22.5" customHeight="1">
+    <row r="5" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>38</v>
       </c>
@@ -1035,7 +1282,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" ht="22.5" customHeight="1">
+    <row r="6" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>46</v>
       </c>
@@ -1067,7 +1314,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="7" ht="22.5" customHeight="1">
+    <row r="7" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>54</v>
       </c>
@@ -1099,7 +1346,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="8" ht="22.5" customHeight="1">
+    <row r="8" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>62</v>
       </c>
@@ -1131,7 +1378,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="9" ht="22.5" customHeight="1">
+    <row r="9" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>70</v>
       </c>
@@ -1163,7 +1410,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="10" ht="22.5" customHeight="1">
+    <row r="10" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>78</v>
       </c>
@@ -1195,7 +1442,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="11" ht="22.5" customHeight="1">
+    <row r="11" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>86</v>
       </c>
@@ -1227,7 +1474,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="12" ht="22.5" customHeight="1">
+    <row r="12" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>94</v>
       </c>
@@ -1259,7 +1506,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="13" ht="22.5" customHeight="1">
+    <row r="13" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>102</v>
       </c>
@@ -1291,7 +1538,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="14" ht="22.5" customHeight="1">
+    <row r="14" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>110</v>
       </c>
@@ -1323,7 +1570,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="15" ht="22.5" customHeight="1">
+    <row r="15" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>118</v>
       </c>
@@ -1355,7 +1602,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="16" ht="22.5" customHeight="1">
+    <row r="16" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>125</v>
       </c>
@@ -1387,7 +1634,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="17" ht="22.5" customHeight="1">
+    <row r="17" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>132</v>
       </c>
@@ -1419,7 +1666,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="18" ht="22.5" customHeight="1">
+    <row r="18" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>139</v>
       </c>
@@ -1451,7 +1698,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="19" ht="22.5" customHeight="1">
+    <row r="19" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>147</v>
       </c>
@@ -1483,7 +1730,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="20" ht="22.5" customHeight="1">
+    <row r="20" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>154</v>
       </c>
@@ -1515,7 +1762,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="21" ht="22.5" customHeight="1">
+    <row r="21" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>161</v>
       </c>
@@ -1547,15 +1794,335 @@
         <v>168</v>
       </c>
     </row>
+    <row r="22" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>246</v>
+      </c>
+    </row>
   </sheetData>
-  <dataValidations>
-    <dataValidation type="list" allowBlank="1" showDropDown="1" showErrorMessage="1" sqref="D2:D21">
-      <formula1>"High,Critical,Medium"</formula1>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" sqref="D2:D31" xr:uid="{00000000-0002-0000-0000-000000000000}">
+      <formula1>"High,Critical,Medium,low"</formula1>
     </dataValidation>
   </dataValidations>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>